--- a/ai_logs/HoangNam_AILogs.xlsx
+++ b/ai_logs/HoangNam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="2"/>
+    <workbookView windowWidth="11520" windowHeight="9720" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="193">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -315,6 +315,27 @@
     <t>005</t>
   </si>
   <si>
+    <t>Code implementation</t>
+  </si>
+  <si>
+    <t>Model Layer / Unit tests</t>
+  </si>
+  <si>
+    <t>Cần triển khai 8 thực thể Java và enum, BaseEntity + toCsvLine()/fromCsvLine(), đồng thời tạo unit test kiểm tra Stock.deduct() và BatchLot.isExpired()</t>
+  </si>
+  <si>
+    <t>Pharmacist, Prescription, PrescriptionItem, DispenseRecord, BatchLot (version). Implement tất cả Enum. Implement BaseEntity + toCsvLine/fromCsvLine. Unit test: Stock.deduct() đúng, BatchLot.isExpired() đúng với ngày hôm nay. 8 Entity classes. Unit test: deduct() và isExpired() pass. Parse/serialize round-trip.”</t>
+  </si>
+  <si>
+    <t>Đã thêm các class model Branch, Medicine, Stock, Pharmacist, Prescription, PrescriptionItem, DispenseRecord, BatchLot, cùng PharmacistRole và PrescriptionStatus. Thêm BaseEntity, toCsvLine()/fromCsvLine() cho mỗi class. Thêm ModelTests.java kiểm tra Stock.deduct(), BatchLot.isExpired(), và round-trip CSV.</t>
+  </si>
+  <si>
+    <t>Ban đầu đã xây xong toàn bộ. Sau đó user thay đổi yêu cầu, tôi đã khôi phục lại Stock và đưa test về trạng thái ban đầu.</t>
+  </si>
+  <si>
+    <t>ModelTests.java, 8 file Java và enum, Base Entity</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -430,6 +451,24 @@
   </si>
   <si>
     <t>Thêm error handling: java try { quantity = Integer.parseInt(parts[3]); } catch (NumberFormatException e) { logger.error("Invalid quantity in line: " + line); quantity = 0; // default safe } Hoặc validate CSV trước parse</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>None / Accurate</t>
+  </si>
+  <si>
+    <t>Đã tạo đầy đủ 8 entity và test, đồng thời compile và chạy kiểm tra thành công</t>
+  </si>
+  <si>
+    <t>Thực tế file model và test đã tồn tại và đã biên dịch chạy được</t>
+  </si>
+  <si>
+    <t>Dựa vào kết quả compile/run terminal có ALL TESTS PASSED</t>
+  </si>
+  <si>
+    <t>Không cần chỉnh sửa; thông tin đúng với kết quả thực tế</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -2125,13 +2164,27 @@
       <c r="A8" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="B8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:8">
       <c r="A9" s="14"/>
@@ -2336,32 +2389,32 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
@@ -2369,19 +2422,19 @@
         <v>56</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="57.6" spans="1:6">
@@ -2389,19 +2442,19 @@
         <v>64</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
@@ -2409,19 +2462,19 @@
         <v>72</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:6">
@@ -2429,19 +2482,19 @@
         <v>80</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:6">
@@ -2449,48 +2502,60 @@
         <v>88</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:6">
       <c r="A9" s="24" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:6">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="A10" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:6">
       <c r="A11" s="14"/>
@@ -2606,73 +2671,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="14" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="14" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="14" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2699,42 +2764,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -2742,13 +2807,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -2756,13 +2821,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
@@ -2770,13 +2835,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>36</v>
@@ -2784,13 +2849,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>36</v>
@@ -2798,32 +2863,32 @@
     </row>
     <row r="12" ht="18" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
@@ -2831,13 +2896,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>36</v>
@@ -2845,13 +2910,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>36</v>
@@ -2859,13 +2924,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>36</v>
@@ -2873,13 +2938,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>36</v>
@@ -2887,27 +2952,27 @@
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
@@ -2915,13 +2980,13 @@
         <v>48</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/HoangNam_AILogs.xlsx
+++ b/ai_logs/HoangNam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9720" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="21000" windowHeight="8520" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="255">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -336,6 +336,120 @@
     <t>ModelTests.java, 8 file Java và enum, Base Entity</t>
   </si>
   <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Fix/Refactor</t>
+  </si>
+  <si>
+    <t>MainView - menu flow</t>
+  </si>
+  <si>
+    <t>Sau khi login, menu bị thoát sớm hoặc không quay lại đúng menu case; cần console chạy liên tục và có “Press Enter” trước khi về menu.</t>
+  </si>
+  <si>
+    <t>“Sau khi hoàn thành việc trong console, thay vì trực tiếp về menu thì hiện nhấn enter để về menu”</t>
+  </si>
+  <si>
+    <t>Đã thêm vòng lặp cho menu vai trò và helper pause để sau mỗi thao tác xong thì hiện Press Enter to return to menu... rồi mới quay lại menu.</t>
+  </si>
+  <si>
+    <t>Luồng console ổn định hơn, người dùng kiểm soát được nhịp thao tác và không bị rơi ra khỏi chương trình.</t>
+  </si>
+  <si>
+    <t>MainView.java</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>Controller layer</t>
+  </si>
+  <si>
+    <t>Cần bổ sung các file controller để xử lý nghiệp vụ chính của hệ thống, gồm xuất thuốc, stock, report và luồng menu liên quan.</t>
+  </si>
+  <si>
+    <t>Tạo các file LoginController, DispensedController, StockController, MedicineController, ReportCOntroller theo yêu cầu dưới đây:"..."</t>
+  </si>
+  <si>
+    <t>Đã tạo và nối các controller cần thiết cho luồng xuất thuốc, xem stock, báo cáo và xử lý menu console; đồng thời gắn chúng với repository tương ứng.</t>
+  </si>
+  <si>
+    <t>Tách rõ xử lý nghiệp vụ khỏi UI, giúp code dễ bảo trì và mở rộng hơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DispensedController, StockController, MedicineController, ReportController</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>MainView + ReportController - Manager reports</t>
+  </si>
+  <si>
+    <t>Cần thêm report cho manager: View near expiry warning và Sale report, ban đầu theo branch, sau đó điều chỉnh để nhập branch ID.</t>
+  </si>
+  <si>
+    <t>“Thêm phần View Near expiry warning và sale report... Nó nằm trong phần managerMenu...”</t>
+  </si>
+  <si>
+    <t>Đã bổ sung case 3 và 4 trong manager menu; thêm hàm report hiển thị batch sắp hết hạn và doanh số theo branch ID.</t>
+  </si>
+  <si>
+    <t>Báo cáo quản lý có lọc theo chi nhánh, đúng yêu cầu thực tế hơn và sát use case hơn.</t>
+  </si>
+  <si>
+    <t>MainView.java, ReportController.java</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>MainView - Pharmacist menu</t>
+  </si>
+  <si>
+    <t>Cần thêm Medicine management vào menu pharmacist, với 3 chức năng: thêm, sửa, xóa thuốc trong stoc</t>
+  </si>
+  <si>
+    <t>“Tạo phần này cho tôi, nó sẽ nằm case số 4... Thêm thuốc... Sửa thuốc...”</t>
+  </si>
+  <si>
+    <t>Đã tạo submenu Medicine management trong pharmacist menu; thêm flow nhập dữ liệu, gọi controller để lưu/sửa/xóa stock.</t>
+  </si>
+  <si>
+    <t>Phần quản lý thuốc được chuyển vào đúng vai trò sử dụng, tách rõ nghiệp vụ và UI.</t>
+  </si>
+  <si>
+    <t>MainView.java, StockController.java, StockRepository.java</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>Gap Analysis</t>
+  </si>
+  <si>
+    <t>Controller layer - T5 coverage</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra project còn thiếu gì so với T5: controller, end-to-end dispense, tồn kho, dispense record.</t>
+  </si>
+  <si>
+    <t>“T5 ⚙ Controller Layer... Project trong này có còn thiếu sót so với yêu cầu ở trên không”</t>
+  </si>
+  <si>
+    <t>Chỉ ra còn thiếu DispenseCalculator, PharmacistController, test end-to-end thật sự cho luồng xuất thuốc; processDispense() và ReportController đã có nhưng test end-to-end chưa hoàn chỉnh.</t>
+  </si>
+  <si>
+    <t>Giúp xác định rõ khoảng trống còn lại để hoàn thiện đúng tiêu chí T5 thay vì chỉ có code rời rạc.</t>
+  </si>
+  <si>
+    <t>DispenseController.java, StockController.java, ReportController.java, RepositoryTests.java</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -435,9 +549,6 @@
     <t>Tách 2 check: java public String getAvailabilityStatus() { if (isExpired()) return "HẾT HẠN"; if (quantity == 0) return "HẾT HÀNG"; return "CÒN HÀNG"; } Hoặc exception riêng: ExpiredBatchException vs OutOfStockException</t>
   </si>
   <si>
-    <t>006</t>
-  </si>
-  <si>
     <t>Missing Error Handling</t>
   </si>
   <si>
@@ -453,9 +564,6 @@
     <t>Thêm error handling: java try { quantity = Integer.parseInt(parts[3]); } catch (NumberFormatException e) { logger.error("Invalid quantity in line: " + line); quantity = 0; // default safe } Hoặc validate CSV trước parse</t>
   </si>
   <si>
-    <t>007</t>
-  </si>
-  <si>
     <t>None / Accurate</t>
   </si>
   <si>
@@ -469,6 +577,84 @@
   </si>
   <si>
     <t>Không cần chỉnh sửa; thông tin đúng với kết quả thực tế</t>
+  </si>
+  <si>
+    <t>Missing Component / Overclaim</t>
+  </si>
+  <si>
+    <t>T5 controller layer đã đủ để đáp ứng yêu cầu</t>
+  </si>
+  <si>
+    <t>Trong repo vẫn thiếu DispenseCalculator và PharmacistController, nên chưa khớp đầy đủ yêu cầu T5</t>
+  </si>
+  <si>
+    <t>Quét toàn bộ controller và util, không thấy 2 class này</t>
+  </si>
+  <si>
+    <t>Báo rõ phần còn thiếu và bổ sung 2 class này nếu cần đúng chuẩn T5</t>
+  </si>
+  <si>
+    <t>Incomplete End-to-End Test</t>
+  </si>
+  <si>
+    <t>Luồng xuất thuốc đã được test end-to-end đầy đủ</t>
+  </si>
+  <si>
+    <t>Hiện chỉ có test rời rạc cho repository, chưa có test gọi DispenseController.processDispense() rồi kiểm tra đồng thời tồn kho và DispenseRecord</t>
+  </si>
+  <si>
+    <t>Đọc RepositoryTests.java và ModelTests.java</t>
+  </si>
+  <si>
+    <t>Tạo test tích hợp cho 1 đơn thuốc: xuất thành công, stock giảm đúng, record được ghi đúng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UI Flow Mismatch</t>
+  </si>
+  <si>
+    <t>Case 3 trong pharmacist menu sẽ mở đúng phần stock/report</t>
+  </si>
+  <si>
+    <t>Có lúc case 3 bị trỏ nhầm sang managerMenu, không đúng flow nghiệp vụ ban đầu</t>
+  </si>
+  <si>
+    <t>So sánh yêu cầu người dùng với MainView.java khi review lại menu</t>
+  </si>
+  <si>
+    <t>Tách riêng submenu đúng vai trò và chỉ cho case 3 mở menu stock/report cần thiết</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unnecessary Input</t>
+  </si>
+  <si>
+    <t>Case 3 cần nhập branch ID ngay từ menu chính</t>
+  </si>
+  <si>
+    <t>branch ID nên nhập trong submenu con, không nên nhập ngay ở case 3 nếu mục đó chỉ là menu chuyển hướng</t>
+  </si>
+  <si>
+    <t>Người dùng phản hồi trực tiếp và mình đối chiếu lại MainView.java</t>
+  </si>
+  <si>
+    <t>Bỏ input thừa ở menu chính, chuyển việc nhập branch ID vào từng chức năng con</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>Scope Confusion</t>
+  </si>
+  <si>
+    <t>View near expiry warning và Sale report có thể chạy chung không cần phân theo branch</t>
+  </si>
+  <si>
+    <t>Người dùng yêu cầu cả hai phần này phải nhập và lọc theo branch ID</t>
+  </si>
+  <si>
+    <t>Đối chiếu lại yêu cầu sau khi sửa ReportController</t>
+  </si>
+  <si>
+    <t>Cập nhật hàm report nhận branch ID và lọc dữ liệu theo chi nhánh tương ứng</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -638,7 +824,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +915,11 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
@@ -1234,137 +1425,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1412,10 +1603,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1789,7 +1983,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -1797,7 +1991,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -1805,7 +1999,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
@@ -1813,7 +2007,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
@@ -1826,7 +2020,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -1834,30 +2028,30 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21" t="e">
+      <c r="C12" s="22" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="23" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1956,7 +2150,7 @@
       <c r="A24" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="24">
         <v>0</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1967,7 +2161,7 @@
       <c r="A25" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="24">
         <v>0</v>
       </c>
       <c r="C25" s="13" t="s">
@@ -1978,7 +2172,7 @@
       <c r="A26" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="24">
         <v>0</v>
       </c>
       <c r="C26" s="13" t="s">
@@ -1989,7 +2183,7 @@
       <c r="A27" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="24">
         <v>0</v>
       </c>
       <c r="C27" s="13" t="s">
@@ -2135,7 +2329,7 @@
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="25" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="14" t="s">
@@ -2161,7 +2355,7 @@
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:8">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>88</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -2187,57 +2381,139 @@
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:8">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+      <c r="A9" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:8">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+      <c r="A10" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:8">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+      <c r="A11" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:8">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+      <c r="A12" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:8">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="A13" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:8">
-      <c r="A14" s="14"/>
+      <c r="A14" s="25" t="s">
+        <v>133</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -2389,213 +2665,273 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" ht="57.6" spans="1:6">
+      <c r="A5" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:6">
+      <c r="A6" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:6">
+      <c r="A7" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:6">
+      <c r="A8" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:6">
+      <c r="A9" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:6">
+      <c r="A10" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" ht="57.6" spans="1:6">
-      <c r="A5" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="B10" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:6">
+      <c r="A11" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1" spans="1:6">
-      <c r="A6" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:6">
+      <c r="A12" s="25" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="7" ht="60" customHeight="1" spans="1:6">
-      <c r="A7" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1" spans="1:6">
-      <c r="A8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:6">
+      <c r="A13" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1" spans="1:6">
-      <c r="A9" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:6">
+      <c r="A14" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1" spans="1:6">
-      <c r="A10" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1" spans="1:6">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" ht="60" customHeight="1" spans="1:6">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" ht="60" customHeight="1" spans="1:6">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" ht="60" customHeight="1" spans="1:6">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1" spans="1:6">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="A15" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:6">
       <c r="A16" s="14"/>
@@ -2671,73 +3007,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="14" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="14" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="14" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2764,42 +3100,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -2807,13 +3143,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -2821,13 +3157,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
@@ -2835,13 +3171,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>36</v>
@@ -2849,13 +3185,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>36</v>
@@ -2863,32 +3199,32 @@
     </row>
     <row r="12" ht="18" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
@@ -2896,13 +3232,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>36</v>
@@ -2910,13 +3246,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>36</v>
@@ -2924,13 +3260,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>36</v>
@@ -2938,13 +3274,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>36</v>
@@ -2952,27 +3288,27 @@
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
@@ -2980,13 +3316,13 @@
         <v>48</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/HoangNam_AILogs.xlsx
+++ b/ai_logs/HoangNam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="8520" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="21000" windowHeight="9180" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
+    <t>R</t>
   </si>
   <si>
     <t>2</t>
@@ -824,7 +824,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,6 +869,11 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Wingdings 2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1425,137 +1430,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1576,13 +1581,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1591,25 +1599,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1983,7 +1991,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -1991,7 +1999,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -1999,7 +2007,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
@@ -2007,7 +2015,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
@@ -2020,7 +2028,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -2028,30 +2036,30 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="22" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22" t="e">
+      <c r="C12" s="23" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="22" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2075,58 +2083,58 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2147,46 +2155,46 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="25">
         <v>0</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="25">
         <v>0</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="25">
         <v>0</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="25">
         <v>0</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2220,7 +2228,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2251,396 +2259,396 @@
       </c>
     </row>
     <row r="4" ht="100" customHeight="1" spans="1:8">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="15" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" ht="100" customHeight="1" spans="1:8">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1" spans="1:8">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:8">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:8">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="15" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:8">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="15" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:8">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="15" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:8">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="15" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:8">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:8">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:8">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:8">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:8">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" ht="80" customHeight="1" spans="1:8">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" ht="80" customHeight="1" spans="1:8">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" ht="80" customHeight="1" spans="1:8">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:8">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
     </row>
     <row r="22" ht="80" customHeight="1" spans="1:8">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
     </row>
     <row r="23" ht="80" customHeight="1" spans="1:8">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24" ht="80" customHeight="1" spans="1:8">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
     </row>
     <row r="25" ht="80" customHeight="1" spans="1:8">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
     </row>
     <row r="26" ht="80" customHeight="1" spans="1:8">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2664,12 +2672,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:6">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2694,316 +2702,316 @@
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" ht="57.6" spans="1:6">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:6">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:6">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:6">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:6">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:6">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="15" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" spans="1:6">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="15" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:6">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:6">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" spans="1:6">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:6">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" ht="60" customHeight="1" spans="1:6">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:6">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" ht="60" customHeight="1" spans="1:6">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" ht="60" customHeight="1" spans="1:6">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:6">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" ht="60" customHeight="1" spans="1:6">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" ht="60" customHeight="1" spans="1:6">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" ht="60" customHeight="1" spans="1:6">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
@@ -3011,68 +3019,68 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="15" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="15" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="15" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3134,7 +3142,7 @@
       <c r="B6" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -3148,7 +3156,7 @@
       <c r="B7" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -3162,7 +3170,7 @@
       <c r="B8" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -3176,7 +3184,7 @@
       <c r="B9" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -3190,7 +3198,7 @@
       <c r="B10" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -3223,7 +3231,7 @@
       <c r="B14" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -3237,7 +3245,7 @@
       <c r="B15" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -3251,7 +3259,7 @@
       <c r="B16" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -3265,7 +3273,7 @@
       <c r="B17" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -3279,7 +3287,7 @@
       <c r="B18" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -3287,17 +3295,17 @@
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:4">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>249</v>
       </c>
     </row>
@@ -3307,63 +3315,63 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>36</v>
       </c>
     </row>

--- a/ai_logs/HoangNam_AILogs.xlsx
+++ b/ai_logs/HoangNam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="9180" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9708" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="280">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -450,6 +450,51 @@
     <t>011</t>
   </si>
   <si>
+    <t>Code Design</t>
+  </si>
+  <si>
+    <t>Admin View Integration</t>
+  </si>
+  <si>
+    <t>Cần một phần Admin riêng để quản lý nhân sự, chi nhánh và doanh thu trong hệ thống nhà thuốc.</t>
+  </si>
+  <si>
+    <t>Thiết kế AdminView và AdminController để quản lý pharmacist, branch và báo cáo doanh thu, tách riêng khỏi luồng của pharmacist.</t>
+  </si>
+  <si>
+    <t>Tạo menu Admin riêng với CRUD staff, CRUD branch có bảo vệ khi xóa, và báo cáo doanh thu theo 30 ngày / toàn thời gian.</t>
+  </si>
+  <si>
+    <t>Mình xác nhận rằng trách nhiệm của Admin khác hoàn toàn với phần quản lý thuốc của pharmacist. Vì vậy mình tách logic admin ra controller/view riêng để rõ ràng và dễ bảo trì hơn.</t>
+  </si>
+  <si>
+    <t>AdminController.java; AdminView.java</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>Main Routing / Role Handling</t>
+  </si>
+  <si>
+    <t>Cần tích hợp Admin view vào luồng chạy chính mà không làm hỏng đăng nhập hiện có.</t>
+  </si>
+  <si>
+    <t>Gắn menu Admin vào MainView và đảm bảo routing theo role vẫn hoạt động sau khi thêm controller mới.</t>
+  </si>
+  <si>
+    <t>Cập nhật wiring để user ADMIN mở AdminView, còn STAFF vẫn dùng menu pharmacist.</t>
+  </si>
+  <si>
+    <t>Mình kiểm tra lại phân quyền sau refactor và giữ nguyên đăng nhập bằng số điện thoại. Luồng admin được nạp qua dependency injection nên giảm coupling.</t>
+  </si>
+  <si>
+    <t>Main.java; MainView.java; User.java</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -639,9 +684,6 @@
     <t>Bỏ input thừa ở menu chính, chuyển việc nhập branch ID vào từng chức năng con</t>
   </si>
   <si>
-    <t>012</t>
-  </si>
-  <si>
     <t>Scope Confusion</t>
   </si>
   <si>
@@ -657,6 +699,42 @@
     <t>Cập nhật hàm report nhận branch ID và lọc dữ liệu theo chi nhánh tương ứng</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Oversimplification</t>
+  </si>
+  <si>
+    <t>AI cho rằng chỉ cần thêm một menu mới ở tầng UI là đủ để có Admin view.</t>
+  </si>
+  <si>
+    <t>Thực tế còn cần controller riêng, ràng buộc xóa branch, và logic tổng hợp doanh thu, không chỉ là một màn hình menu.</t>
+  </si>
+  <si>
+    <t>So sánh gợi ý của AI với kế hoạch triển khai và trách nhiệm thực tế của Admin trong codebase.</t>
+  </si>
+  <si>
+    <t>Tạo AdminController/AdminView, thêm bảo vệ khi quản lý branch, và giữ logic doanh thu ngoài UI layer.</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Context Misunderstanding</t>
+  </si>
+  <si>
+    <t>AI ban đầu trộn lẫn trách nhiệm của Admin với phần quản lý thuốc.</t>
+  </si>
+  <si>
+    <t>Admin trong project này quản lý staff, branch và doanh thu; còn CRUD thuốc thuộc về MedicineController riêng.</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại cấu trúc menu và ranh giới giữa các controller sau refactor.</t>
+  </si>
+  <si>
+    <t>Tách MedicineController khỏi StockController và giữ phần Admin chỉ tập trung vào nghiệp vụ quản trị.</t>
+  </si>
+  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -703,9 +781,6 @@
   </si>
   <si>
     <t>Old API syntax, deprecated methods</t>
-  </si>
-  <si>
-    <t>Context Misunderstanding</t>
   </si>
   <si>
     <t>AI không hiểu đúng bối cảnh</t>
@@ -2522,23 +2597,53 @@
       <c r="A14" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:8">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="A15" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:8">
       <c r="A16" s="15"/>
@@ -2673,32 +2778,32 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="16" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="17" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
@@ -2706,19 +2811,19 @@
         <v>56</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" ht="57.6" spans="1:6">
@@ -2726,19 +2831,19 @@
         <v>64</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
@@ -2746,19 +2851,19 @@
         <v>72</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:6">
@@ -2766,19 +2871,19 @@
         <v>80</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:6">
@@ -2786,19 +2891,19 @@
         <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:6">
@@ -2806,19 +2911,19 @@
         <v>96</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:6">
@@ -2826,19 +2931,19 @@
         <v>104</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:6">
@@ -2846,19 +2951,19 @@
         <v>111</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" spans="1:6">
@@ -2866,19 +2971,19 @@
         <v>118</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:6">
@@ -2886,19 +2991,19 @@
         <v>125</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:6">
@@ -2906,56 +3011,80 @@
         <v>133</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" spans="1:6">
       <c r="A15" s="26" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:6">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="A16" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1" spans="1:6">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="A17" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:6">
       <c r="A18" s="15"/>
@@ -3015,73 +3144,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="13" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="15" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="15" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="15" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="15" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="15" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3108,42 +3237,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -3151,13 +3280,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -3165,13 +3294,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
@@ -3179,13 +3308,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>36</v>
@@ -3193,13 +3322,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>36</v>
@@ -3207,32 +3336,32 @@
     </row>
     <row r="12" ht="18" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
@@ -3240,13 +3369,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>36</v>
@@ -3254,13 +3383,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>36</v>
@@ -3268,13 +3397,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>36</v>
@@ -3282,13 +3411,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>36</v>
@@ -3296,27 +3425,27 @@
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="9" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="10" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="10" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
@@ -3324,13 +3453,13 @@
         <v>48</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:4">
